--- a/5_evaluation_results/ablation_conditions/2_quality_radar/quality_radar_datasheet.xlsx
+++ b/5_evaluation_results/ablation_conditions/2_quality_radar/quality_radar_datasheet.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Hypothesis Integration &amp; Specificity</t>
+          <t>Hypothesis Specificity</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Hypothesis Integration &amp; Specificity</t>
+          <t>Hypothesis Specificity</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Hypothesis Integration &amp; Specificity</t>
+          <t>Hypothesis Specificity</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Hypothesis Integration &amp; Specificity</t>
+          <t>Hypothesis Specificity</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Hypothesis Integration &amp; Specificity</t>
+          <t>Hypothesis Specificity</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
